--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,10 +493,10 @@
         <v>6.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>38.95</v>
+        <v>38.94</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32.22</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="3">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:38</t>
+    <t xml:space="preserve">2026-10-05 04:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>6.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>38.94</v>
+        <v>38.95</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>32.23</v>
